--- a/astro-site/public/dl/ghost-kitchen-checklist-templates/05-cloud-kitchen-cleaning-checklist-inventory-maintenance.xlsx
+++ b/astro-site/public/dl/ghost-kitchen-checklist-templates/05-cloud-kitchen-cleaning-checklist-inventory-maintenance.xlsx
@@ -732,7 +732,7 @@
     <row r="6" ht="63" customHeight="1">
       <c r="B6" s="24" t="inlineStr">
         <is>
-          <t>▸ The "Quarterly &amp; Annual" tab covers the maintenance you CONTRACT out and that gets asked for in an inspection: pest control, hood and ductwork cleaning (NFPA 96), extinguishers and hood fire suppression, gas, legionella, refrigeration, used cooking oil, cardboard and plastic packaging pickup, thermometer calibration, insurance, app contracts and sales tax.</t>
+          <t>▸ The "Quarterly &amp; Annual" tab covers the maintenance you CONTRACT out and that gets asked for in an inspection: pest control, hood and ductwork cleaning (NFPA 96), extinguishers and hood fire suppression, gas, legionella, refrigeration, used cooking oil, cardboard and plastic packaging pickup, grease trap, thermometer calibration, insurance, app contracts and sales tax.</t>
         </is>
       </c>
     </row>
@@ -1326,11 +1326,11 @@
       <c r="B24" s="8" t="n"/>
       <c r="C24" s="9" t="inlineStr">
         <is>
-          <t>qt</t>
+          <t>pt</t>
         </is>
       </c>
       <c r="D24" s="9" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="E24" s="10">
         <f>IF(B24="","",IF(B24&lt;D24,"⚠️ REORDER","OK"))</f>
@@ -1347,11 +1347,11 @@
       <c r="B25" s="12" t="n"/>
       <c r="C25" s="13" t="inlineStr">
         <is>
-          <t>qt</t>
+          <t>pt</t>
         </is>
       </c>
       <c r="D25" s="13" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="E25" s="14">
         <f>IF(B25="","",IF(B25&lt;D25,"⚠️ REORDER","OK"))</f>
@@ -1389,11 +1389,11 @@
       <c r="B27" s="12" t="n"/>
       <c r="C27" s="13" t="inlineStr">
         <is>
-          <t>qt</t>
+          <t>pt</t>
         </is>
       </c>
       <c r="D27" s="13" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="E27" s="14">
         <f>IF(B27="","",IF(B27&lt;D27,"⚠️ REORDER","OK"))</f>
@@ -1898,7 +1898,7 @@
       </c>
       <c r="B9" s="37" t="inlineStr">
         <is>
-          <t>Cutting boards: wash, rinse and sanitize (approved sanitizer at label strength, test strip; FDA 4-501.114)</t>
+          <t>Cutting boards: deep clean and inspect — scrub, sanitize (approved sanitizer at label strength, test strip; FDA 4-501.114) and resurface or replace any with deep cuts or stains (in use they are washed, rinsed and sanitized at least every 4 h, FDA 4-602.11)</t>
         </is>
       </c>
       <c r="C9" s="29" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="B14" s="38" t="inlineStr">
         <is>
-          <t>Check the fryer oil (color, smell, smoke) and log the date of the last change; change it per the fryer manufacturer's instructions</t>
+          <t>Check the fryer oil with a TPM tester or test strips (color, smell and smoke only as a backup) and log the date of the last change; no federal limit: change it when the tester says and per the fryer manufacturer</t>
         </is>
       </c>
       <c r="C14" s="29" t="inlineStr">
@@ -2634,7 +2634,7 @@
       <c r="F28" s="40" t="n"/>
       <c r="G28" s="41" t="n"/>
     </row>
-    <row r="29" ht="49" customHeight="1">
+    <row r="29" ht="61.25" customHeight="1">
       <c r="A29" s="20" t="n"/>
       <c r="B29" s="34" t="inlineStr">
         <is>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="D29" s="39" t="inlineStr">
         <is>
-          <t>Fat goes rancid even frozen; freezing only counts as parasite destruction at −4 °F or below for 7 days (or −31 °F or below until solid plus 15 h), with a record (FDA 3-402.11): a regular 0 °F freezer does not get there</t>
+          <t>Fat goes rancid even frozen; freezing only counts as parasite destruction at −4 °F or below for 7 days, or at −31 °F until solid and then 15 h at −31 °F or 24 h at −4 °F (FDA 3-402.11), with a record or the supplier's statement (FDA 3-402.12): a regular 0 °F freezer does not get there</t>
         </is>
       </c>
       <c r="E29" s="40" t="n"/>
@@ -2927,7 +2927,7 @@
       </c>
       <c r="B7" s="37" t="inlineStr">
         <is>
-          <t>Full fryer oil change and deep clean (boil-out) per the fryer manufacturer's instructions (many have built-in filtration designed for hot oil; others need it cooled), with heat-resistant gloves, apron and goggles; used oil goes to the used cooking oil recycler's container; keep the pickup receipt</t>
+          <t>Fryer check per the manufacturer: thermostat and high-limit, drain valve, baskets and the built-in filtration or filter machine; the oil itself is changed whenever the TPM tester says (no federal limit), not once a month — the boil-out is weekly ("Weekly Deep Clean" tab)</t>
         </is>
       </c>
       <c r="C7" s="29" t="inlineStr">
@@ -3443,7 +3443,7 @@
       </c>
       <c r="B7" s="37" t="inlineStr">
         <is>
-          <t>Hood and duct cleaning by a certified contractor (NFPA 96): quarterly if high volume (cooking all day, wok or charbroil), semiannual if moderate</t>
+          <t>Hood and duct cleaning by a certified contractor (NFPA 96): quarterly if high volume (24-hour cooking, charbroiling or wok), semiannual if moderate — a multi-brand kitchen cooking from morning to night often goes quarterly: your hood contractor and fire marshal decide</t>
         </is>
       </c>
       <c r="C7" s="29" t="n"/>
@@ -3466,7 +3466,7 @@
       </c>
       <c r="B8" s="38" t="inlineStr">
         <is>
-          <t>Annual extinguisher maintenance by a licensed fire protection company: new tag and record (OSHA 1910.157); hood fire suppression inspected every 6 months (NFPA 96); hydrostatic tests as the label says (OSHA 1910.157(f))</t>
+          <t>Hood fire suppression inspected every 6 months (NFPA 96) and annual extinguisher maintenance by a licensed fire protection company: new tag and record (OSHA 1910.157); hydrostatic tests as the label says (OSHA 1910.157(f))</t>
         </is>
       </c>
       <c r="C8" s="29" t="n"/>
@@ -3477,7 +3477,7 @@
       </c>
       <c r="E8" s="29" t="inlineStr">
         <is>
-          <t>Annual</t>
+          <t>Semiannual</t>
         </is>
       </c>
       <c r="F8" s="30" t="n"/>
@@ -3571,7 +3571,7 @@
       </c>
       <c r="B13" s="37" t="inlineStr">
         <is>
-          <t>Used fryer oil pickup by a licensed recycler: file the pickup receipts</t>
+          <t>Used fryer oil: pickups by a licensed recycler as often as your volume needs; every quarter, check the receipts are on file and the outdoor container is closed and not leaking</t>
         </is>
       </c>
       <c r="C13" s="29" t="n"/>
@@ -3594,7 +3594,7 @@
       </c>
       <c r="B14" s="38" t="inlineStr">
         <is>
-          <t>Cardboard and plastic packaging pickup by your waste and recycling hauler: contract current and receipts filed (a ghost kitchen goes through far more packaging than a regular restaurant)</t>
+          <t>Review the cardboard and plastic recycling contract with your hauler (pickups usually run weekly or more: a ghost kitchen goes through far more packaging than a regular restaurant) and keep the grease trap pumping manifests, as often as your local FOG rules require</t>
         </is>
       </c>
       <c r="C14" s="29" t="n"/>
@@ -3617,7 +3617,7 @@
       </c>
       <c r="B15" s="37" t="inlineStr">
         <is>
-          <t>Calibrate thermometers and probes against a known reference (ice-point method, 32 °F)</t>
+          <t>Once a year, have the oven and griddle thermostats and any built-in probes checked against a known standard; the probe thermometers get an ice-point check (32 °F) at opening (Hot Station tab in 02, task #1) and after any drop</t>
         </is>
       </c>
       <c r="C15" s="29" t="n"/>
